--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Diagonal Reforma</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bryan Flores</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0006']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bryan Flores</t>
+          <t>Jesus Morales</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0006']</t>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0010']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0010']</t>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004', 'TPM-0005']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004', 'TPM-0005']</t>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004', 'TPM-0006', 'TPM-0005', 'TPM-0009']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Luis Quintana</t>
+          <t>Bryan Flors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004', 'TPM-0006', 'TPM-0005', 'TPM-0009']</t>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bryan Flors</t>
+          <t>Jesus Morales</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0004']</t>
+          <t>['TPM-0001', 'TPM-0003', 'TPM-0002', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['TPM-0001', 'TPM-0003', 'TPM-0002', 'TPM-0004']</t>
+          <t>['TPM-0001', 'TPM-0003', 'TPM-0002', 'TPM-0004', 'TPM-0005', 'TPM-0006']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,46 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>['TPM-0001', 'TPM-0003', 'TPM-0002', 'TPM-0004', 'TPM-0005', 'TPM-0006']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E0028</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>['TPM-0005', 'TPM-0006', 'TPM-0007']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,86 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0003', 'TPM-0002', 'TPM-0004', 'TPM-0005', 'TPM-0006']</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>E0028</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>['TPM-0005', 'TPM-0006', 'TPM-0007']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jesus Morales</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0003']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Jesus Morales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bryan Flores</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0003', 'TPM-0004', 'TPM-0009', 'TPM-0010']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bryan Flores</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0003', 'TPM-0004', 'TPM-0009', 'TPM-0010']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0006']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,46 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0006']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E0028</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>['TPM-0007', 'TPM-0008']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,46 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>['TPM-0007', 'TPM-0008']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E0029</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>['TPM-0009', 'TPM-0011', 'TPM-0010', 'TPM-0012']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,126 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0006']</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>E0028</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>['TPM-0007', 'TPM-0008']</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>E0029</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>['TPM-0009', 'TPM-0011', 'TPM-0010', 'TPM-0012']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,126 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0006']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E0028</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>['TPM-0007', 'TPM-0008']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E0029</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>['TPM-0009', 'TPM-0011', 'TPM-0010', 'TPM-0012']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,46 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>['TPM-0009', 'TPM-0011', 'TPM-0010', 'TPM-0012']</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E0030</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>['TPM-0013', 'TPM-0015', 'TPM-0014', 'TPM-0017']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,166 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0004', 'TPM-0003', 'TPM-0005', 'TPM-0006']</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>E0028</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>['TPM-0007', 'TPM-0008']</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>E0029</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>['TPM-0009', 'TPM-0011', 'TPM-0010', 'TPM-0012']</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>E0030</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>['TPM-0013', 'TPM-0015', 'TPM-0014', 'TPM-0017']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0036']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0036']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,46 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E0027</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['TPM-0001', 'TPM-0002', 'TPM-0003', 'TPM-0004']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Tarimas_Asociadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E0027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['TPM-0182', 'TPM-0183', 'TPM-0184', 'TPM-0185']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,46 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>['TPM-0182', 'TPM-0183', 'TPM-0184', 'TPM-0185']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E0028</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>['TPM-0186']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,46 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>['TPM-0186']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E0029</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>['TPM-0213']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,46 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>['TPM-0213']</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E0030</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>['TPM-0077', 'TPM-0078']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,46 +575,6 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>['TPM-0213']</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>E0030</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>['TPM-0077', 'TPM-0078']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,46 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>['TPM-0213']</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E0030</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>['TPM-0258']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,46 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>['TPM-0258']</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E0031</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bryan Flores</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>['TPM-0259', 'TPM-0260']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,6 +655,46 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>['TPM-0259', 'TPM-0260']</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>E0032</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>['TPM-0263']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,46 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>['TPM-0263']</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E0033</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>['TPM-0269']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,46 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E0034</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>['TPM-0233']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,46 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E0035</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>['TPM-0202', 'TPM-0265', 'TPM-0253', 'TPM-0205', 'TPM-0191', 'TPM-0222', 'TPM-0204', 'TPM-0256']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,46 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>E0035</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>['TPM-0202', 'TPM-0265', 'TPM-0253', 'TPM-0205', 'TPM-0191', 'TPM-0222', 'TPM-0204', 'TPM-0256']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,46 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E0035</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Inde 714, Parque Industrial II, 35079 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>['TPM-0191', 'TPM-0204', 'TPM-0205', 'TPM-0222', 'TPM-0253', 'TPM-0256', 'TPM-0265', 'TPM-0202']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E0036</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>['TPM-0187', 'TPM-0188', 'TPM-0214', 'TPM-0255']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,46 +818,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>E0036</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>['TPM-0187', 'TPM-0188', 'TPM-0214', 'TPM-0255']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E0036</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cruz Carreon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Inde 714, Parque Industrial II, 35079 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>['TPM-0188', 'TPM-0187', 'TPM-0214', 'TPM-0255']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,6 +858,46 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E0037</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>['TPM-0272', 'TPM-0271']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,46 +858,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>E0037</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>['TPM-0272', 'TPM-0271']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,6 +858,46 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E0037</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calle Inde 714, 35079 Gómez Palacio, Durango </t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>['TPM-0271', 'TPM-0272']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,46 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>E0038</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calle Inde 714, 35079 Gómez Palacio, Durango </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>['TPM-0273']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,6 +938,46 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E0039</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>['TPM-0274']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,6 +978,46 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E0040</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calle Inde 714, 35079 Gómez Palacio, Durango </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>['TPM-0279']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,966 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E0001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>["TPM-0280", "TPM-0281", "TPM-0282", "TPM-0283", "TPM-0284", "TPM-0285", "TPM-0286", "TPM-0287", "TPM-0288", "TPM-0289", "TPM-0290", "TPM-0291", "TPM-0292", "TPM-0293", "TPM-0294", "TPM-0295", "TPM-0296", "TPM-0297", "TPM-0298", "TPM-0299", "TPM-0300", "TPM-0301", "TPM-0302", "TPM-0303"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E0002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>["TPM-0304", "TPM-0305", "TPM-0306", "TPM-0307", "TPM-0308", "TPM-0309", "TPM-0310", "TPM-0311", "TPM-0312", "TPM-0313", "TPM-0314", "TPM-0315", "TPM-0316", "TPM-0317", "TPM-0318", "TPM-0319"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E0003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>["TPM-0320"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>E0004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>["TPM-0321", "TPM-0322", "TPM-0323", "TPM-0324", "TPM-0325"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>E0005</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>["TPM-0326", "TPM-0327", "TPM-0328", "TPM-0329", "TPM-0330", "TPM-0331"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>E0007</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>["TPM-0332", "TPM-0333", "TPM-0334", "TPM-0335", "TPM-0336", "TPM-0337", "TPM-0338", "TPM-0339", "TPM-0340", "TPM-0341", "TPM-0342", "TPM-0343", "TPM-0344", "TPM-0345", "TPM-0353", "TPM-0367"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>E0006</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>["TPM-0346", "TPM-0347", "TPM-0348", "TPM-0349", "TPM-0350", "TPM-0351", "TPM-0352"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>E0008</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>["TPM-0354"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>E0009</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>["TPM-0355", "TPM-0361", "TPM-0362", "TPM-0363", "TPM-0364", "TPM-0365", "TPM-0366"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>E0010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>["TPM-0356", "TPM-0368", "TPM-0369", "TPM-0370", "TPM-0371", "TPM-0372", "TPM-0373", "TPM-0385", "TPM-0386", "TPM-0387", "TPM-0388", "TPM-0389"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>E0011</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>["TPM-0357", "TPM-0374", "TPM-0375", "TPM-0376", "TPM-0377", "TPM-0378", "TPM-0379"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>E0012</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>["TPM-0358"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>E0013</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>["TPM-0359"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>E0014</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>["TPM-0360", "TPM-0380", "TPM-0381", "TPM-0382", "TPM-0383", "TPM-0384", "TPM-0390", "TPM-0391", "TPM-0392", "TPM-0393", "TPM-0394", "TPM-0395", "TPM-0396"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>E0015</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>["TPM-0397", "TPM-0398", "TPM-0399", "TPM-0400", "TPM-0401", "TPM-0402"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>E0016</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>["TPM-0403", "TPM-0404", "TPM-0405", "TPM-0406", "TPM-0407", "TPM-0408", "TPM-0409", "TPM-0411", "TPM-0412"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>E0017</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>["TPM-0410"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>E0018</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>["TPM-0413", "TPM-0414", "TPM-0415", "TPM-0416", "TPM-0417", "TPM-0418", "TPM-0419", "TPM-0420", "TPM-0421", "TPM-0422"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>E0019</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>["TPM-0423", "TPM-0424", "TPM-0425", "TPM-0426", "TPM-0427", "TPM-0428", "TPM-0429"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>E0020</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>["TPM-0430", "TPM-0431", "TPM-0432", "TPM-0433"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>E0021</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>["TPM-0434", "TPM-0435", "TPM-0436", "TPM-0437", "TPM-0438", "TPM-0439", "TPM-0440", "TPM-0441"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>E0022</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>["TPM-0442", "TPM-0443", "TPM-0444"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E0023</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>["TPM-0445", "TPM-0446", "TPM-0447", "TPM-0448", "TPM-0449", "TPM-0450", "TPM-0451", "TPM-0452", "TPM-0453", "TPM-0454"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>E0024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>["TPM-0455", "TPM-0456", "TPM-0457", "TPM-0458", "TPM-0459"]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,966 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>E0001</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>["TPM-0280", "TPM-0281", "TPM-0282", "TPM-0283", "TPM-0284", "TPM-0285", "TPM-0286", "TPM-0287", "TPM-0288", "TPM-0289", "TPM-0290", "TPM-0291", "TPM-0292", "TPM-0293", "TPM-0294", "TPM-0295", "TPM-0296", "TPM-0297", "TPM-0298", "TPM-0299", "TPM-0300", "TPM-0301", "TPM-0302", "TPM-0303"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>E0002</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>["TPM-0304", "TPM-0305", "TPM-0306", "TPM-0307", "TPM-0308", "TPM-0309", "TPM-0310", "TPM-0311", "TPM-0312", "TPM-0313", "TPM-0314", "TPM-0315", "TPM-0316", "TPM-0317", "TPM-0318", "TPM-0319"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>E0003</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>["TPM-0320"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>E0004</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>["TPM-0321", "TPM-0322", "TPM-0323", "TPM-0324", "TPM-0325"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>E0005</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>["TPM-0326", "TPM-0327", "TPM-0328", "TPM-0329", "TPM-0330", "TPM-0331"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>E0007</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>["TPM-0332", "TPM-0333", "TPM-0334", "TPM-0335", "TPM-0336", "TPM-0337", "TPM-0338", "TPM-0339", "TPM-0340", "TPM-0341", "TPM-0342", "TPM-0343", "TPM-0344", "TPM-0345", "TPM-0353", "TPM-0367"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>E0006</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>["TPM-0346", "TPM-0347", "TPM-0348", "TPM-0349", "TPM-0350", "TPM-0351", "TPM-0352"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>E0008</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>["TPM-0354"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>E0009</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>["TPM-0355", "TPM-0361", "TPM-0362", "TPM-0363", "TPM-0364", "TPM-0365", "TPM-0366"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>E0010</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>["TPM-0356", "TPM-0368", "TPM-0369", "TPM-0370", "TPM-0371", "TPM-0372", "TPM-0373", "TPM-0385", "TPM-0386", "TPM-0387", "TPM-0388", "TPM-0389"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>E0011</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>["TPM-0357", "TPM-0374", "TPM-0375", "TPM-0376", "TPM-0377", "TPM-0378", "TPM-0379"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>E0012</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>["TPM-0358"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>E0013</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>["TPM-0359"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>E0014</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>["TPM-0360", "TPM-0380", "TPM-0381", "TPM-0382", "TPM-0383", "TPM-0384", "TPM-0390", "TPM-0391", "TPM-0392", "TPM-0393", "TPM-0394", "TPM-0395", "TPM-0396"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>E0015</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>["TPM-0397", "TPM-0398", "TPM-0399", "TPM-0400", "TPM-0401", "TPM-0402"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>E0016</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>["TPM-0403", "TPM-0404", "TPM-0405", "TPM-0406", "TPM-0407", "TPM-0408", "TPM-0409", "TPM-0411", "TPM-0412"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>E0017</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>["TPM-0410"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>E0018</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>["TPM-0413", "TPM-0414", "TPM-0415", "TPM-0416", "TPM-0417", "TPM-0418", "TPM-0419", "TPM-0420", "TPM-0421", "TPM-0422"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>E0019</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>["TPM-0423", "TPM-0424", "TPM-0425", "TPM-0426", "TPM-0427", "TPM-0428", "TPM-0429"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>E0020</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>["TPM-0430", "TPM-0431", "TPM-0432", "TPM-0433"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>E0021</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>["TPM-0434", "TPM-0435", "TPM-0436", "TPM-0437", "TPM-0438", "TPM-0439", "TPM-0440", "TPM-0441"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>E0022</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>["TPM-0442", "TPM-0443", "TPM-0444"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>E0023</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>["TPM-0445", "TPM-0446", "TPM-0447", "TPM-0448", "TPM-0449", "TPM-0450", "TPM-0451", "TPM-0452", "TPM-0453", "TPM-0454"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>E0024</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Carga Historica</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>["TPM-0455", "TPM-0456", "TPM-0457", "TPM-0458", "TPM-0459"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,966 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E0001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>["TPM-0001", "TPM-0002", "TPM-0003", "TPM-0004", "TPM-0005", "TPM-0006", "TPM-0007", "TPM-0008", "TPM-0009", "TPM-0010", "TPM-0011", "TPM-0012", "TPM-0013", "TPM-0014", "TPM-0015", "TPM-0016", "TPM-0017", "TPM-0018", "TPM-0019", "TPM-0020", "TPM-0021", "TPM-0022", "TPM-0023", "TPM-0024"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E0002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>["TPM-0025", "TPM-0026", "TPM-0027", "TPM-0028", "TPM-0029", "TPM-0030", "TPM-0031", "TPM-0032", "TPM-0033", "TPM-0034", "TPM-0035", "TPM-0036", "TPM-0037", "TPM-0038", "TPM-0039", "TPM-0040"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E0003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>["TPM-0041"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>E0004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>["TPM-0042", "TPM-0043", "TPM-0044", "TPM-0045", "TPM-0046"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>E0005</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>["TPM-0047", "TPM-0048", "TPM-0049", "TPM-0050", "TPM-0051", "TPM-0052"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>E0007</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>["TPM-0053", "TPM-0054", "TPM-0055", "TPM-0056", "TPM-0057", "TPM-0058", "TPM-0059", "TPM-0060", "TPM-0061", "TPM-0062", "TPM-0063", "TPM-0064", "TPM-0065", "TPM-0066", "TPM-0074", "TPM-0088"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>E0006</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>["TPM-0067", "TPM-0068", "TPM-0069", "TPM-0070", "TPM-0071", "TPM-0072", "TPM-0073"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>E0008</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>["TPM-0075"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>E0009</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>["TPM-0076", "TPM-0082", "TPM-0083", "TPM-0084", "TPM-0085", "TPM-0086", "TPM-0087"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>E0010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>["TPM-0077", "TPM-0089", "TPM-0090", "TPM-0091", "TPM-0092", "TPM-0093", "TPM-0094", "TPM-0106", "TPM-0107", "TPM-0108", "TPM-0109", "TPM-0110"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>E0011</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>["TPM-0078", "TPM-0095", "TPM-0096", "TPM-0097", "TPM-0098", "TPM-0099", "TPM-0100"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>E0012</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>["TPM-0079"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>E0013</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>["TPM-0080"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>E0014</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>["TPM-0081", "TPM-0101", "TPM-0102", "TPM-0103", "TPM-0104", "TPM-0105", "TPM-0111", "TPM-0112", "TPM-0113", "TPM-0114", "TPM-0115", "TPM-0116", "TPM-0117"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>E0015</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>["TPM-0118", "TPM-0119", "TPM-0120", "TPM-0121", "TPM-0122", "TPM-0123"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>E0016</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>["TPM-0124", "TPM-0125", "TPM-0126", "TPM-0127", "TPM-0128", "TPM-0129", "TPM-0130", "TPM-0132", "TPM-0133"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>E0017</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>["TPM-0131"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>E0018</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>["TPM-0134", "TPM-0135", "TPM-0136", "TPM-0137", "TPM-0138", "TPM-0139", "TPM-0140", "TPM-0141", "TPM-0142", "TPM-0143"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>E0019</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>["TPM-0144", "TPM-0145", "TPM-0146", "TPM-0147", "TPM-0148", "TPM-0149", "TPM-0150"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>E0020</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>["TPM-0151", "TPM-0152", "TPM-0153", "TPM-0154"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>E0021</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>["TPM-0155", "TPM-0156", "TPM-0157", "TPM-0158", "TPM-0159", "TPM-0160", "TPM-0161", "TPM-0162"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>E0022</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>["TPM-0163", "TPM-0164", "TPM-0165"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E0023</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>["TPM-0166", "TPM-0167", "TPM-0168", "TPM-0169", "TPM-0170", "TPM-0171", "TPM-0172", "TPM-0173", "TPM-0174", "TPM-0175"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>E0024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Carga Historica</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>["TPM-0176", "TPM-0177", "TPM-0178", "TPM-0179", "TPM-0180"]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,11 +1037,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1077,11 +1073,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1117,11 +1109,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1157,11 +1145,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1197,11 +1181,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1237,11 +1217,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1277,11 +1253,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1317,11 +1289,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1357,11 +1325,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1397,11 +1361,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1437,11 +1397,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1477,11 +1433,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1517,11 +1469,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1557,11 +1505,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1597,11 +1541,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1637,11 +1577,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1677,11 +1613,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1717,11 +1649,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1757,11 +1685,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1797,11 +1721,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1837,11 +1757,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1877,11 +1793,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1917,11 +1829,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1957,11 +1865,7 @@
           <t>Carga Historica</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>Galvatec Industrias</t>
@@ -1975,6 +1879,46 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>["TPM-0176", "TPM-0177", "TPM-0178", "TPM-0179", "TPM-0180"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>E0065</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>['TPM-0283', 'TPM-0282', 'TPM-0281']</t>
         </is>
       </c>
     </row>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,6 +1922,46 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>E0066</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>['TPM-0284']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1962,6 +1962,46 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>E0067</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>['TPM-0288', 'TPM-0287', 'TPM-0286', 'TPM-0285']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1962,46 +1962,6 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>E0067</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>COVISA</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>['TPM-0288', 'TPM-0287', 'TPM-0286', 'TPM-0285']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1962,6 +1962,46 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>E0067</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>COVISA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>['TPM-0288', 'TPM-0287', 'TPM-0286', 'TPM-0285']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2002,6 +2002,46 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>E0068</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>YPC</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Julio Verne s.n, San Agustín, 27013 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>['TPM-0289']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,6 +2042,46 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>E0069</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>['TPM-0290']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,6 +2082,46 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>E0070</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>['TPM-0296', 'TPM-0295', 'TPM-0294', 'TPM-0293', 'TPM-0292', 'TPM-0291']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2122,6 +2122,46 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>E0071</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>['TPM-0215', 'TPM-0246', 'TPM-0247', 'TPM-0249', 'TPM-0297']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Galvatec Industrias</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,46 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>E0072</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>['TPM-0298']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2202,6 +2202,46 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>E0073</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>['TPM-0299']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,6 +2242,46 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>E0074</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>['TPM-0304', 'TPM-0303', 'TPM-0302', 'TPM-0301', 'TPM-0300']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2282,6 +2282,46 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>E0075</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>['TPM-0305']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2322,6 +2322,46 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>E0076</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>['TPM-0314']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2362,6 +2362,46 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>E0077</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>['TPM-0322']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,6 +2402,46 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>E0078</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>['TPM-0329', 'TPM-0330', 'TPM-0331', 'TPM-0332', 'TPM-0333', 'TPM-0334']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,6 +2442,46 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>E0079</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>['TPM-0335', 'TPM-0336', 'TPM-0337', 'TPM-0338']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2482,6 +2482,46 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>E0080</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>['TPM-0339', 'TPM-0340', 'TPM-0341', 'TPM-0342', 'TPM-0343', 'TPM-0344']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2522,46 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>E0081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>['TPM-0346']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,6 +2562,46 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>E0082</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>['TPM-0345', 'TPM-0347', 'TPM-0348', 'TPM-0349', 'TPM-0350', 'TPM-0351']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2602,6 +2602,46 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>E0083</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>['TPM-0267']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2642,6 +2642,46 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>E0084</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>['TPM-0200']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2682,46 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>E0085</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>['TPM-0352', 'TPM-0353', 'TPM-0354', 'TPM-0355', 'TPM-0356', 'TPM-0357']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,6 +2722,46 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>E0086</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>['TPM-0358', 'TPM-0359', 'TPM-0360', 'TPM-0381', 'TPM-0382', 'TPM-0383']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2762,46 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>E0087</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Meccano</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Antonio Duenes Orozco 170, Cd Industrial, 27019 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>['TPM-0384', 'TPM-0386', 'TPM-0385']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2802,46 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>E0088</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Meccano</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Antonio Duenes Orozco 170, Cd Industrial, 27019 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>['TPM-0395', 'TPM-0394', 'TPM-0393', 'TPM-0392', 'TPM-0391', 'TPM-0390', 'TPM-0389']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,46 +2802,6 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>E0088</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Meccano</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Antonio Duenes Orozco 170, Cd Industrial, 27019 Torreón, Coah.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>['TPM-0395', 'TPM-0394', 'TPM-0393', 'TPM-0392', 'TPM-0391', 'TPM-0390', 'TPM-0389']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2802,46 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>E0088</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>['TPM-0364', 'TPM-0374', 'TPM-0375', 'TPM-0377', 'TPM-0376', 'TPM-0363']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2842,6 +2842,46 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>E0089</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>['TPM-0389', 'TPM-0390', 'TPM-0391', 'TPM-0392', 'TPM-0393', 'TPM-0394', 'TPM-0395']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,6 +2882,46 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>E0090</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carretera Torreón, Blvr. Mieleras 163 Ote, Sta Sofía, 27293 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>['TPM-0428']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +2922,46 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>E0091</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>['TPM-0439']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,46 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>E0092</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>['TPM-0378', 'TPM-0373', 'TPM-0408', 'TPM-0402', 'TPM-0429', 'TPM-0427']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3002,6 +3002,46 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>E0093</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>['TPM-0309', 'TPM-0311', 'TPM-0317']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,6 +3042,46 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>E0094</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>['TPM-0380', 'TPM-0396', 'TPM-0398', 'TPM-0420', 'TPM-0424', 'TPM-0426']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3082,6 +3082,46 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>E0095</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>['TPM-0219', 'TPM-0220']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3122,6 +3122,46 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>E0096</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>['TPM-0361', 'TPM-0362', 'TPM-0365', 'TPM-0403', 'TPM-0430', 'TPM-0431']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3162,6 +3162,46 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>E0097</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>['TPM-0228', 'TPM-0229', 'TPM-0230', 'TPM-0241', 'TPM-0264', 'TPM-0275']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3202,6 +3202,46 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>E0098</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>['TPM-0411', 'TPM-0416', 'TPM-0419', 'TPM-0421', 'TPM-0422', 'TPM-0423']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3242,6 +3242,46 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>E0099</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>['TPM-0227']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3282,6 +3282,46 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>E0100</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>['TPM-0216', 'TPM-0240', 'TPM-0251']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3322,6 +3322,46 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>E0101</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>['TPM-0412', 'TPM-0413', 'TPM-0414', 'TPM-0415', 'TPM-0418', 'TPM-0404']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3362,6 +3362,46 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>E0102</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>['TPM-0268', 'TPM-0277', 'TPM-0310']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3402,6 +3402,46 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>E0103</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>['TPM-0379', 'TPM-0447', 'TPM-0425', 'TPM-0406', 'TPM-0405', 'TPM-0410']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3402,46 +3402,6 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>E0103</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>EQM</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>['TPM-0379', 'TPM-0447', 'TPM-0425', 'TPM-0406', 'TPM-0405', 'TPM-0410']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3402,6 +3402,46 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>E0103</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>['TPM-0379', 'TPM-0405', 'TPM-0406', 'TPM-0409', 'TPM-0410', 'TPM-0425']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3442,6 +3442,46 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>E0104</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>['TPM-0308', 'TPM-0313', 'TPM-0321']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3482,6 +3482,46 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>E0105</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>['TPM-0232', 'TPM-0235', 'TPM-0319']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,6 +3522,46 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>E0106</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>['TPM-0218', 'TPM-0245', 'TPM-0244', 'TPM-0243', 'TPM-0223', 'TPM-0250']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3562,6 +3562,46 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>E0107</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>['TPM-0315', 'TPM-0312', 'TPM-0307']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3602,6 +3602,46 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>E0108</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>['TPM-0459', 'TPM-0407', 'TPM-0417', 'TPM-0387', 'TPM-0399', 'TPM-0397']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3642,6 +3642,46 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>E0109</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>['TPM-0462', 'TPM-0461']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3682,6 +3682,46 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>E0110</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>['TPM-0318', 'TPM-0316', 'TPM-0207']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3604,11 +3604,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E0108</t>
+          <t>E0109</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3638,17 +3638,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['TPM-0459', 'TPM-0407', 'TPM-0417', 'TPM-0387', 'TPM-0399', 'TPM-0397']</t>
+          <t>['TPM-0462', 'TPM-0461']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>E0109</t>
+          <t>E0110</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3668,55 +3668,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
-        <is>
-          <t>['TPM-0462', 'TPM-0461']</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>E0110</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>PLANTA RIO XIX</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
         <is>
           <t>['TPM-0318', 'TPM-0316', 'TPM-0207']</t>
         </is>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3682,6 +3682,46 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>E0111</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>['TPM-0387', 'TPM-0397', 'TPM-0399', 'TPM-0407', 'TPM-0417']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3722,6 +3722,46 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>E0112</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>['TPM-0459']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,6 +3762,46 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>E0113</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>['TPM-0466', 'TPM-0465', 'TPM-0464', 'TPM-0463']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,16 +2764,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>E0087</t>
+          <t>E0088</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2788,37 +2788,37 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Meccano</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Antonio Duenes Orozco 170, Cd Industrial, 27019 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['TPM-0384', 'TPM-0386', 'TPM-0385']</t>
+          <t>['TPM-0364', 'TPM-0374', 'TPM-0375', 'TPM-0377', 'TPM-0376', 'TPM-0363']</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>E0088</t>
+          <t>E0089</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Luis Quintana</t>
+          <t>Practicante Dual</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2838,27 +2838,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>['TPM-0364', 'TPM-0374', 'TPM-0375', 'TPM-0377', 'TPM-0376', 'TPM-0363']</t>
+          <t>['TPM-0389', 'TPM-0390', 'TPM-0391', 'TPM-0392', 'TPM-0393', 'TPM-0394', 'TPM-0395']</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>E0089</t>
+          <t>E0090</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Practicante Dual</t>
+          <t>Luis Quintana</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2868,32 +2868,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>kirbymex</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carretera Torreón, Blvr. Mieleras 163 Ote, Sta Sofía, 27293 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>['TPM-0389', 'TPM-0390', 'TPM-0391', 'TPM-0392', 'TPM-0393', 'TPM-0394', 'TPM-0395']</t>
+          <t>['TPM-0428']</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>E0090</t>
+          <t>E0091</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2908,27 +2908,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>kirbymex</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carretera Torreón, Blvr. Mieleras 163 Ote, Sta Sofía, 27293 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>['TPM-0428']</t>
+          <t>['TPM-0439']</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>E0091</t>
+          <t>E0092</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2958,22 +2958,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>['TPM-0439']</t>
+          <t>['TPM-0378', 'TPM-0373', 'TPM-0408', 'TPM-0402', 'TPM-0429', 'TPM-0427']</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>E0092</t>
+          <t>E0093</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2988,27 +2988,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>['TPM-0378', 'TPM-0373', 'TPM-0408', 'TPM-0402', 'TPM-0429', 'TPM-0427']</t>
+          <t>['TPM-0309', 'TPM-0311', 'TPM-0317']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>E0093</t>
+          <t>E0094</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3028,27 +3028,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>['TPM-0309', 'TPM-0311', 'TPM-0317']</t>
+          <t>['TPM-0380', 'TPM-0396', 'TPM-0398', 'TPM-0420', 'TPM-0424', 'TPM-0426']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>E0094</t>
+          <t>E0095</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['TPM-0380', 'TPM-0396', 'TPM-0398', 'TPM-0420', 'TPM-0424', 'TPM-0426']</t>
+          <t>['TPM-0219', 'TPM-0220']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>E0095</t>
+          <t>E0096</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3108,27 +3108,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['TPM-0219', 'TPM-0220']</t>
+          <t>['TPM-0361', 'TPM-0362', 'TPM-0365', 'TPM-0403', 'TPM-0430', 'TPM-0431']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>E0096</t>
+          <t>E0097</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3148,27 +3148,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['TPM-0361', 'TPM-0362', 'TPM-0365', 'TPM-0403', 'TPM-0430', 'TPM-0431']</t>
+          <t>['TPM-0228', 'TPM-0229', 'TPM-0230', 'TPM-0241', 'TPM-0264', 'TPM-0275']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>E0097</t>
+          <t>E0098</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3188,27 +3188,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['TPM-0228', 'TPM-0229', 'TPM-0230', 'TPM-0241', 'TPM-0264', 'TPM-0275']</t>
+          <t>['TPM-0411', 'TPM-0416', 'TPM-0419', 'TPM-0421', 'TPM-0422', 'TPM-0423']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>E0098</t>
+          <t>E0099</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3228,27 +3228,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>['TPM-0411', 'TPM-0416', 'TPM-0419', 'TPM-0421', 'TPM-0422', 'TPM-0423']</t>
+          <t>['TPM-0227']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>E0099</t>
+          <t>E0100</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3278,17 +3278,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['TPM-0227']</t>
+          <t>['TPM-0216', 'TPM-0240', 'TPM-0251']</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>E0100</t>
+          <t>E0101</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3308,27 +3308,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['TPM-0216', 'TPM-0240', 'TPM-0251']</t>
+          <t>['TPM-0412', 'TPM-0413', 'TPM-0414', 'TPM-0415', 'TPM-0418', 'TPM-0404']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>E0101</t>
+          <t>E0102</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['TPM-0412', 'TPM-0413', 'TPM-0414', 'TPM-0415', 'TPM-0418', 'TPM-0404']</t>
+          <t>['TPM-0268', 'TPM-0277', 'TPM-0310']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>E0102</t>
+          <t>E0103</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3388,27 +3388,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['TPM-0268', 'TPM-0277', 'TPM-0310']</t>
+          <t>['TPM-0379', 'TPM-0405', 'TPM-0406', 'TPM-0409', 'TPM-0410', 'TPM-0425']</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>E0103</t>
+          <t>E0104</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3428,27 +3428,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>['TPM-0379', 'TPM-0405', 'TPM-0406', 'TPM-0409', 'TPM-0410', 'TPM-0425']</t>
+          <t>['TPM-0308', 'TPM-0313', 'TPM-0321']</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E0104</t>
+          <t>E0105</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3478,17 +3478,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['TPM-0308', 'TPM-0313', 'TPM-0321']</t>
+          <t>['TPM-0232', 'TPM-0235', 'TPM-0319']</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>E0105</t>
+          <t>E0106</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3518,17 +3518,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>['TPM-0232', 'TPM-0235', 'TPM-0319']</t>
+          <t>['TPM-0218', 'TPM-0245', 'TPM-0244', 'TPM-0243', 'TPM-0223', 'TPM-0250']</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>E0106</t>
+          <t>E0107</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['TPM-0218', 'TPM-0245', 'TPM-0244', 'TPM-0243', 'TPM-0223', 'TPM-0250']</t>
+          <t>['TPM-0315', 'TPM-0312', 'TPM-0307']</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>E0107</t>
+          <t>E0109</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['TPM-0315', 'TPM-0312', 'TPM-0307']</t>
+          <t>['TPM-0462', 'TPM-0461']</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E0109</t>
+          <t>E0110</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3628,27 +3628,27 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['TPM-0462', 'TPM-0461']</t>
+          <t>['TPM-0318', 'TPM-0316', 'TPM-0207']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>E0110</t>
+          <t>E0111</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3668,32 +3668,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PLANTA RIO XIX</t>
+          <t>EQM</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['TPM-0318', 'TPM-0316', 'TPM-0207']</t>
+          <t>['TPM-0387', 'TPM-0397', 'TPM-0399', 'TPM-0407', 'TPM-0417']</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>E0111</t>
+          <t>E0112</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3718,22 +3718,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['TPM-0387', 'TPM-0397', 'TPM-0399', 'TPM-0407', 'TPM-0417']</t>
+          <t>['TPM-0459']</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E0112</t>
+          <t>E0113</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3748,55 +3748,15 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>EQM</t>
+          <t>PLANTA RIO XIX</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
-        <is>
-          <t>['TPM-0459']</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>87</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>E0113</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>13/08/2026</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>PLANTA RIO XIX</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
         <is>
           <t>['TPM-0466', 'TPM-0465', 'TPM-0464', 'TPM-0463']</t>
         </is>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,6 +3762,46 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>88</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>E0114</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>['TPM-0400', 'TPM-0401', 'TPM-0388', 'TPM-0385', 'TPM-0384', 'TPM-0386']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3802,6 +3802,46 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>89</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>E0115</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>['TPM-0467']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,6 +3842,46 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>90</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>E0116</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>['TPM-0468']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,46 +3842,6 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>90</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>E0116</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>EQM</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>['TPM-0468']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3882,6 +3882,46 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>91</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>E0117</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>['TPM-0488', 'TPM-0487', 'TPM-0486']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3922,6 +3922,46 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>92</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>E0118</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>['TPM-0323', 'TPM-0324', 'TPM-0325', 'TPM-0447', 'TPM-0445', 'TPM-0436']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,6 +3962,46 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>93</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>E0119</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Practicante Dual</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>['TPM-0434', 'TPM-0435', 'TPM-0432', 'TPM-0437', 'TPM-0433', 'TPM-0442']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,46 +3962,6 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>93</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>E0119</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Practicante Dual</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Galvatec Industrias</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Prol. Valle Guadiana 919, Parque Industrial II, 35078 Gómez Palacio, Dgo.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>['TPM-0434', 'TPM-0435', 'TPM-0432', 'TPM-0437', 'TPM-0433', 'TPM-0442']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,6 +3962,46 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>93</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>E0119</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>['TPM-0434', 'TPM-0435', 'TPM-0437', 'TPM-0432', 'TPM-0433', 'TPM-0442']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4002,6 +4002,46 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>94</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>E0120</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>['TPM-0446', 'TPM-0441', 'TPM-0438', 'TPM-0491', 'TPM-0490', 'TPM-0489']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4042,6 +4042,46 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>95</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>E0121</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>['TPM-0440', 'TPM-0443']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4082,6 +4082,46 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>96</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>E0122</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>['TPM-0497']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4122,6 +4122,46 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>97</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>E0123</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>['TPM-0505']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4162,6 +4162,46 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>98</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>E0124</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>['TPM-0508']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4202,6 +4202,46 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>99</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>E0125</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>['TPM-0510', 'TPM-0509', 'TPM-0507', 'TPM-0493', 'TPM-0494', 'TPM-0495', 'TPM-0496', 'TPM-0504']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4242,6 +4242,46 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>100</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>E0126</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>['TPM-0513', 'TPM-0512', 'TPM-0511']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4242,46 +4242,6 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>100</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>E0126</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>25/08/2026</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Luis Quintana</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Metales</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>EQM</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>['TPM-0513', 'TPM-0512', 'TPM-0511']</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4242,6 +4242,46 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>100</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>E0126</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>['TPM-0513', 'TPM-0512', 'TPM-0511']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4282,6 +4282,46 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>101</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>E0127</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Cruz Carreon</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>['TPM-0236', 'TPM-0238', 'TPM-0270', 'TPM-0503', 'TPM-0192', 'TPM-0194']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4322,6 +4322,46 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>102</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>E0128</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>['TPM-0499', 'TPM-0225', 'TPM-0492', 'TPM-0210', 'TPM-0506', 'TPM-0209']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4362,6 +4362,46 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>103</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>E0129</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>['TPM-0514']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4402,6 +4402,46 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>104</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>E0130</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>['TPM-0521', 'TPM-0520', 'TPM-0519', 'TPM-0518', 'TPM-0517', 'TPM-0516', 'TPM-0515']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4442,6 +4442,46 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>105</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>E0131</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>['TPM-0276', 'TPM-0327', 'TPM-0502', 'TPM-0498', 'TPM-0328', 'TPM-0501']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4482,6 +4482,46 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>106</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>E0132</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>['TPM-0522', 'TPM-0456', 'TPM-0444', 'TPM-0326', 'TPM-0500', 'TPM-0211']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4522,6 +4522,46 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>107</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>E0133</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>['TPM-0523']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4562,6 +4562,46 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>108</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>E0134</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carlos Salinas de Gortari 43, Nueva Laguna Nte., 27110 Torreón, Coah.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>['TPM-0524', 'TPM-0539', 'TPM-0525', 'TPM-0526', 'TPM-0540']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Datos_Generales_Remision.xlsx
+++ b/BD_Datos_Generales_Remision.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4642,6 +4642,46 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>110</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>E0136</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Metales</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Calle Inde 714, 35079 Gómez Palacio, Durango</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>['TPM-0556']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
